--- a/summary_semiannually.xlsx
+++ b/summary_semiannually.xlsx
@@ -535,16 +535,16 @@
         <v>0.09384533666554851</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0001126583328709199</v>
+        <v>0.01216759282239608</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9350111082646302</v>
+        <v>0.5552577451290347</v>
       </c>
       <c r="E5" t="n">
         <v>0.3624435417799479</v>
       </c>
       <c r="F5" t="n">
-        <v>0.07737937508325386</v>
+        <v>0.1303008843876718</v>
       </c>
       <c r="G5" t="n">
         <v>0.02455688621167888</v>
@@ -563,16 +563,16 @@
         <v>0.08378808363315637</v>
       </c>
       <c r="C6" t="n">
-        <v>7.393896855881286e-05</v>
+        <v>0.01215075613075574</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9377388525466632</v>
+        <v>0.5562533108982969</v>
       </c>
       <c r="E6" t="n">
         <v>0.3147098263645244</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0664292857780741</v>
+        <v>0.1119873284357224</v>
       </c>
       <c r="G6" t="n">
         <v>0.02000435494537194</v>
@@ -591,16 +591,16 @@
         <v>0.08823753685110192</v>
       </c>
       <c r="C7" t="n">
-        <v>8.77007314641518e-05</v>
+        <v>0.012575803900767</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9695838705126073</v>
+        <v>0.5751980632239658</v>
       </c>
       <c r="E7" t="n">
         <v>0.3256825673455813</v>
       </c>
       <c r="F7" t="n">
-        <v>0.06883651581753832</v>
+        <v>0.1160344231078945</v>
       </c>
       <c r="G7" t="n">
         <v>0.02231070634897801</v>
@@ -619,16 +619,16 @@
         <v>0.09378038387490384</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0001102539382324595</v>
+        <v>0.01235211668789435</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9515809264721103</v>
+        <v>0.5638429261296622</v>
       </c>
       <c r="E8" t="n">
         <v>0.3574924975271483</v>
       </c>
       <c r="F8" t="n">
-        <v>0.07596371517319567</v>
+        <v>0.1282017014187921</v>
       </c>
       <c r="G8" t="n">
         <v>0.02477113935030474</v>
@@ -647,16 +647,16 @@
         <v>0.09121070465921832</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0001031753816206059</v>
+        <v>0.01207402361887988</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9278759263245645</v>
+        <v>0.5513920380201839</v>
       </c>
       <c r="E9" t="n">
         <v>0.3530381230619532</v>
       </c>
       <c r="F9" t="n">
-        <v>0.07513498439736582</v>
+        <v>0.1264362530467579</v>
       </c>
       <c r="G9" t="n">
         <v>0.02338301434105343</v>
@@ -675,16 +675,16 @@
         <v>0.08921162151534689</v>
       </c>
       <c r="C10" t="n">
-        <v>9.105949546819549e-05</v>
+        <v>0.01246154492928277</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9625564841899843</v>
+        <v>0.5697553773767815</v>
       </c>
       <c r="E10" t="n">
         <v>0.3343851170869321</v>
       </c>
       <c r="F10" t="n">
-        <v>0.07035105078555628</v>
+        <v>0.1188525159955352</v>
       </c>
       <c r="G10" t="n">
         <v>0.02300081485063169</v>
@@ -703,16 +703,16 @@
         <v>0.09462103444975134</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0001129613288618414</v>
+        <v>0.01226717868648481</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9448294851179339</v>
+        <v>0.559805366529586</v>
       </c>
       <c r="E11" t="n">
         <v>0.3662545186659409</v>
       </c>
       <c r="F11" t="n">
-        <v>0.07739626481755371</v>
+        <v>0.1306280314727132</v>
       </c>
       <c r="G11" t="n">
         <v>0.02548473826301288</v>
@@ -731,16 +731,16 @@
         <v>0.09384533666554851</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0002218135906530371</v>
+        <v>0.01259085923887849</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7934693327578825</v>
+        <v>0.5726712173636652</v>
       </c>
       <c r="E12" t="n">
         <v>0.3624435417799479</v>
       </c>
       <c r="F12" t="n">
-        <v>0.09118257286888062</v>
+        <v>0.1263387665727099</v>
       </c>
       <c r="G12" t="n">
         <v>0.04895348524243447</v>
@@ -759,16 +759,16 @@
         <v>0.08378808363315637</v>
       </c>
       <c r="C13" t="n">
-        <v>0.000184734372997981</v>
+        <v>0.01245799422355948</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7876907119394199</v>
+        <v>0.5682336591448881</v>
       </c>
       <c r="E13" t="n">
         <v>0.3147098263645244</v>
       </c>
       <c r="F13" t="n">
-        <v>0.07908347943782339</v>
+        <v>0.1096262448000146</v>
       </c>
       <c r="G13" t="n">
         <v>0.04222086027789835</v>
@@ -787,16 +787,16 @@
         <v>0.08823753685110192</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0002029133635188049</v>
+        <v>0.01283294323509468</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8104312281070567</v>
+        <v>0.5847527778902597</v>
       </c>
       <c r="E14" t="n">
         <v>0.3256825673455813</v>
       </c>
       <c r="F14" t="n">
-        <v>0.08235464419956248</v>
+        <v>0.1141384495508916</v>
       </c>
       <c r="G14" t="n">
         <v>0.04520730674042231</v>
@@ -815,16 +815,16 @@
         <v>0.09378038387490384</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0002222501624848712</v>
+        <v>0.01270801123398725</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8019794471345119</v>
+        <v>0.5780671786855812</v>
       </c>
       <c r="E15" t="n">
         <v>0.3574924975271483</v>
       </c>
       <c r="F15" t="n">
-        <v>0.09013400869691982</v>
+        <v>0.1250470968220982</v>
       </c>
       <c r="G15" t="n">
         <v>0.04894473260767065</v>
@@ -843,16 +843,16 @@
         <v>0.09121070465921832</v>
       </c>
       <c r="C16" t="n">
-        <v>0.000212040100602963</v>
+        <v>0.01244171252244645</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7840926590407238</v>
+        <v>0.5662217436635465</v>
       </c>
       <c r="E16" t="n">
         <v>0.3530381230619532</v>
       </c>
       <c r="F16" t="n">
-        <v>0.088912888602196</v>
+        <v>0.1231248075992527</v>
       </c>
       <c r="G16" t="n">
         <v>0.04641080839376093</v>
@@ -871,16 +871,16 @@
         <v>0.08921162151534689</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0002062002916904824</v>
+        <v>0.0126552496919362</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7998838663334505</v>
+        <v>0.5763654921049893</v>
       </c>
       <c r="E17" t="n">
         <v>0.3343851170869321</v>
       </c>
       <c r="F17" t="n">
-        <v>0.08465836473689634</v>
+        <v>0.1174894420828389</v>
       </c>
       <c r="G17" t="n">
         <v>0.04502303845930654</v>
@@ -899,16 +899,16 @@
         <v>0.09462103444975134</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0002249791531319322</v>
+        <v>0.01254578976654575</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7912913690539799</v>
+        <v>0.5704309947681828</v>
       </c>
       <c r="E18" t="n">
         <v>0.3662545186659409</v>
       </c>
       <c r="F18" t="n">
-        <v>0.09241383881773649</v>
+        <v>0.128194775018034</v>
       </c>
       <c r="G18" t="n">
         <v>0.0486719361755785</v>
@@ -927,16 +927,16 @@
         <v>0.09384533666554851</v>
       </c>
       <c r="C19" t="n">
-        <v>9.719238514642795e-05</v>
+        <v>0.01134960514235349</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8393576957337676</v>
+        <v>0.5179762301115575</v>
       </c>
       <c r="E19" t="n">
         <v>0.3624435417799479</v>
       </c>
       <c r="F19" t="n">
-        <v>0.08619754798360278</v>
+        <v>0.1396793347791952</v>
       </c>
       <c r="G19" t="n">
         <v>0.01599790544319504</v>
@@ -955,16 +955,16 @@
         <v>0.08378808363315637</v>
       </c>
       <c r="C20" t="n">
-        <v>5.771941337385985e-05</v>
+        <v>0.01136049376397631</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8441457919803914</v>
+        <v>0.5202797864706801</v>
       </c>
       <c r="E20" t="n">
         <v>0.3147098263645244</v>
       </c>
       <c r="F20" t="n">
-        <v>0.07379450660398788</v>
+        <v>0.119730429359158</v>
       </c>
       <c r="G20" t="n">
         <v>0.01175986508659914</v>
@@ -983,16 +983,16 @@
         <v>0.08823753685110192</v>
       </c>
       <c r="C21" t="n">
-        <v>7.159110891798013e-05</v>
+        <v>0.01173124299910435</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8706307110804283</v>
+        <v>0.5367096748986065</v>
       </c>
       <c r="E21" t="n">
         <v>0.3256825673455813</v>
       </c>
       <c r="F21" t="n">
-        <v>0.07666025857983484</v>
+        <v>0.1243554542809014</v>
       </c>
       <c r="G21" t="n">
         <v>0.01402499764193888</v>
@@ -1011,16 +1011,16 @@
         <v>0.09378038387490384</v>
       </c>
       <c r="C22" t="n">
-        <v>9.397736068203526e-05</v>
+        <v>0.01154335702641439</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8560040604659446</v>
+        <v>0.5270152325679456</v>
       </c>
       <c r="E22" t="n">
         <v>0.3574924975271483</v>
       </c>
       <c r="F22" t="n">
-        <v>0.08444542006427651</v>
+        <v>0.13716040447361</v>
       </c>
       <c r="G22" t="n">
         <v>0.01624769280906088</v>
@@ -1039,16 +1039,16 @@
         <v>0.09121070465921832</v>
       </c>
       <c r="C23" t="n">
-        <v>8.766737334669057e-05</v>
+        <v>0.01126847884583852</v>
       </c>
       <c r="D23" t="n">
-        <v>0.8334810456922801</v>
+        <v>0.5146878870047733</v>
       </c>
       <c r="E23" t="n">
         <v>0.3530381230619532</v>
       </c>
       <c r="F23" t="n">
-        <v>0.08364430553928462</v>
+        <v>0.1354528540642359</v>
       </c>
       <c r="G23" t="n">
         <v>0.01483599780456926</v>
@@ -1067,16 +1067,16 @@
         <v>0.08921162151534689</v>
       </c>
       <c r="C24" t="n">
-        <v>7.479857820394197e-05</v>
+        <v>0.01163571844982275</v>
       </c>
       <c r="D24" t="n">
-        <v>0.8652056292298914</v>
+        <v>0.5321371312139574</v>
       </c>
       <c r="E24" t="n">
         <v>0.3343851170869321</v>
       </c>
       <c r="F24" t="n">
-        <v>0.07826678169383851</v>
+        <v>0.1272545292014006</v>
       </c>
       <c r="G24" t="n">
         <v>0.01447481586100859</v>
@@ -1095,16 +1095,16 @@
         <v>0.09462103444975134</v>
       </c>
       <c r="C25" t="n">
-        <v>9.663148646509094e-05</v>
+        <v>0.01147119784097288</v>
       </c>
       <c r="D25" t="n">
-        <v>0.8504879308622936</v>
+        <v>0.5235704724380283</v>
       </c>
       <c r="E25" t="n">
         <v>0.3662545186659409</v>
       </c>
       <c r="F25" t="n">
-        <v>0.08598155292277834</v>
+        <v>0.1396684436712118</v>
       </c>
       <c r="G25" t="n">
         <v>0.01668516491452319</v>
